--- a/result/morris/morris_first_inf_ONLY_MAE_N256_seed42.xlsx
+++ b/result/morris/morris_first_inf_ONLY_MAE_N256_seed42.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,65 +453,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.60373263888889</v>
+        <v>-8.259765625000004</v>
       </c>
       <c r="C2" t="n">
-        <v>20.12196180555557</v>
+        <v>17.63823784722222</v>
       </c>
       <c r="D2" t="n">
-        <v>33.73391024425788</v>
+        <v>28.33165990825724</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-9.129340277777786</v>
+        <v>3.031575520833333</v>
       </c>
       <c r="C3" t="n">
-        <v>16.24153645833333</v>
+        <v>15.43630642361112</v>
       </c>
       <c r="D3" t="n">
-        <v>27.14356738294234</v>
+        <v>27.40778834902287</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.080186631944446</v>
+        <v>2.024956597222223</v>
       </c>
       <c r="C4" t="n">
-        <v>15.49251302083334</v>
+        <v>12.20073784722223</v>
       </c>
       <c r="D4" t="n">
-        <v>20.35490404002704</v>
+        <v>18.67788555639928</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.68098958333334</v>
+        <v>3.502278645833335</v>
       </c>
       <c r="C5" t="n">
-        <v>14.84353298611111</v>
+        <v>11.57194010416667</v>
       </c>
       <c r="D5" t="n">
-        <v>18.2949557001746</v>
+        <v>19.72430205343728</v>
       </c>
     </row>
     <row r="6">
@@ -521,125 +521,141 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3169487847222223</v>
+        <v>-0.6768663194444444</v>
       </c>
       <c r="C6" t="n">
-        <v>6.518988715277777</v>
+        <v>8.14366319444445</v>
       </c>
       <c r="D6" t="n">
-        <v>15.76779425135665</v>
+        <v>15.42440643460111</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.367296006944445</v>
+        <v>1.155598958333333</v>
       </c>
       <c r="C7" t="n">
-        <v>2.842990451388889</v>
+        <v>7.032552083333334</v>
       </c>
       <c r="D7" t="n">
-        <v>10.25144219217313</v>
+        <v>12.38221184501468</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>dispersal__wind_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.514539930555556</v>
+        <v>2.360243055555555</v>
       </c>
       <c r="C8" t="n">
-        <v>2.469401041666666</v>
+        <v>4.500000000000002</v>
       </c>
       <c r="D8" t="n">
-        <v>7.05747573483651</v>
+        <v>14.1026956866192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.762478298611111</v>
+        <v>0.9753689236111105</v>
       </c>
       <c r="C9" t="n">
-        <v>2.261176215277778</v>
+        <v>3.345160590277779</v>
       </c>
       <c r="D9" t="n">
-        <v>9.040715773458032</v>
+        <v>15.67191112976793</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09309895833333355</v>
+        <v>-0.6387803819444444</v>
       </c>
       <c r="C10" t="n">
-        <v>2.209635416666667</v>
+        <v>2.850585937500001</v>
       </c>
       <c r="D10" t="n">
-        <v>10.01451868445433</v>
+        <v>7.275409357858707</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dispersal__wind_min</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.3521050347222223</v>
+        <v>-0.7157118055555556</v>
       </c>
       <c r="C11" t="n">
-        <v>1.975802951388889</v>
+        <v>2.368055555555557</v>
       </c>
       <c r="D11" t="n">
-        <v>6.492504497568198</v>
+        <v>7.796900693592584</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6930338541666665</v>
+        <v>0.6525607638888892</v>
       </c>
       <c r="C12" t="n">
-        <v>1.281141493055554</v>
+        <v>1.580078125</v>
       </c>
       <c r="D12" t="n">
-        <v>1.348296059069255</v>
+        <v>5.758994098331389</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>incubation__spl_end</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.08875868055555543</v>
+        <v>0.3311631944444446</v>
       </c>
       <c r="C13" t="n">
-        <v>1.020833333333333</v>
+        <v>0.9581163194444445</v>
       </c>
       <c r="D13" t="n">
-        <v>3.331373895030227</v>
+        <v>1.176306833003864</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sporulation__MP_min</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.06749131944444438</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9572482638888888</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.098548762167806</v>
       </c>
     </row>
   </sheetData>
